--- a/assessment_forms/039_mineral_properties_assessment--assessment_forms.xlsx
+++ b/assessment_forms/039_mineral_properties_assessment--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1191,17 +1191,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mineral_type_choices</t>
+          <t>sample_location_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>staurolite</t>
+          <t>location_1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>staurolite</t>
+          <t>location 1</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>location_1</t>
+          <t>location_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>location_1</t>
+          <t>location 2</t>
         </is>
       </c>
     </row>
@@ -1230,29 +1230,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>location_2</t>
+          <t>location_3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>location_2</t>
+          <t>location 3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>sample_location_choices</t>
+          <t>sample_color_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>location_3</t>
+          <t>color_1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>location_3</t>
+          <t>color 1</t>
         </is>
       </c>
     </row>
@@ -1264,29 +1264,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>color_1</t>
+          <t>color_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>color_1</t>
+          <t>color 2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>sample_color_choices</t>
+          <t>sample_shape_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>color_2</t>
+          <t>shape_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>color_2</t>
+          <t>shape 1</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>shape_1</t>
+          <t>shape_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>shape_1</t>
+          <t>shape 2</t>
         </is>
       </c>
     </row>
@@ -1315,29 +1315,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>shape_2</t>
+          <t>shape_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>shape_2</t>
+          <t>shape 3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>sample_shape_choices</t>
+          <t>sample_texture_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>shape_3</t>
+          <t>texture_1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>shape_3</t>
+          <t>texture 1</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>texture_1</t>
+          <t>texture_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>texture_1</t>
+          <t>texture 2</t>
         </is>
       </c>
     </row>
@@ -1366,12 +1366,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>texture_2</t>
+          <t>texture_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>texture_2</t>
+          <t>texture 3</t>
         </is>
       </c>
     </row>
@@ -1383,29 +1383,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>texture_3</t>
+          <t>texture_4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>texture_3</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>sample_texture_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>texture_4</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>texture_4</t>
+          <t>texture 4</t>
         </is>
       </c>
     </row>
